--- a/artifacts/reports/architecture_tuning_lstm_v1.xlsx
+++ b/artifacts/reports/architecture_tuning_lstm_v1.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02630533219034486</v>
+        <v>0.02634294372670795</v>
       </c>
     </row>
     <row r="14">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67.96202560836294</v>
+        <v>66.83515266249076</v>
       </c>
     </row>
     <row r="16">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>40.32981794985244</v>
+        <v>40.76796179997473</v>
       </c>
     </row>
     <row r="17">
@@ -1038,7 +1038,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1114,19 +1114,19 @@
         <v>0.4955974999103683</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.6562172305647336</v>
+        <v>0.6560983222225333</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.005449558310728107</v>
+        <v>0.005193697222340335</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.6562172305647336</v>
+        <v>0.6560983222225333</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.005449558310728107</v>
+        <v>0.005193697222340335</v>
       </c>
       <c r="AH2" t="n">
-        <v>23.82000439951662</v>
+        <v>23.80651270001545</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1202,31 +1202,31 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0229090707835557</v>
+        <v>0.02288283647516584</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03095397412585692</v>
+        <v>0.03095820841866742</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.517823962689854</v>
+        <v>1.517340273475212</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5160058145289814</v>
+        <v>0.5273339110168891</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3593156472165395</v>
+        <v>0.3688642944438875</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.003248872228949848</v>
+        <v>0.002982194444484776</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3593156472165395</v>
+        <v>0.3688642944438875</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.003248872228949848</v>
+        <v>0.002982194444484776</v>
       </c>
       <c r="AH3" t="n">
-        <v>13.05232270003762</v>
+        <v>13.3864735999814</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1302,31 +1302,31 @@
         <v>20</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04526260267618217</v>
+        <v>0.04551551390821578</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05883608945363561</v>
+        <v>0.05922351927863698</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.930609001885168</v>
+        <v>2.984057578068402</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5656374661627831</v>
+        <v>0.5436787536440352</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2370049639009974</v>
+        <v>0.2086646833332553</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.001967730547120381</v>
+        <v>0.001698883332816574</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2370049639009974</v>
+        <v>0.2086646833332553</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001967730547120381</v>
+        <v>0.001698883332816574</v>
       </c>
       <c r="AH4" t="n">
-        <v>8.60301700013224</v>
+        <v>7.573088399978587</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1414,19 +1414,19 @@
         <v>0.4952109184808861</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.112581994442735</v>
+        <v>1.022782708333479</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01298607499403361</v>
+        <v>0.01179879999876397</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.112581994442735</v>
+        <v>1.022782708333479</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01298607499403361</v>
+        <v>0.01179879999876397</v>
       </c>
       <c r="AH5" t="n">
-        <v>40.52045049972367</v>
+        <v>37.24493429996073</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1502,31 +1502,31 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02305557405202937</v>
+        <v>0.02304555264523576</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0310473530116646</v>
+        <v>0.03107475459726162</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.525400014013107</v>
+        <v>1.52667760921712</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5160406506396431</v>
+        <v>0.5192464269133042</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.6051192388856886</v>
+        <v>0.5270807111123252</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.007087636118133864</v>
+        <v>0.006088794444723235</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.6051192388856886</v>
+        <v>0.5270807111123252</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.007087636118133864</v>
+        <v>0.006088794444723235</v>
       </c>
       <c r="AH6" t="n">
-        <v>22.03944750013761</v>
+        <v>19.19410220005375</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1602,31 +1602,31 @@
         <v>20</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.04574416318638141</v>
+        <v>0.04555148313884066</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05918972290383807</v>
+        <v>0.05887962736489399</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.940032417631977</v>
+        <v>2.941698523910825</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.5350814153505182</v>
+        <v>0.5293089633656992</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.4106991555535286</v>
+        <v>0.2662579333328823</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.00629956945582914</v>
+        <v>0.003376238886832855</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.4106991555535286</v>
+        <v>0.2662579333328823</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.00629956945582914</v>
+        <v>0.003376238886832855</v>
       </c>
       <c r="AH7" t="n">
-        <v>15.01195410033688</v>
+        <v>9.706830199909746</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1714,19 +1714,19 @@
         <v>0.4846378208348345</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.795600558343318</v>
+        <v>2.439494866665983</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0299641222130352</v>
+        <v>0.02705727222281792</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.795600558343318</v>
+        <v>2.439494866665983</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0299641222130352</v>
+        <v>0.02705727222281792</v>
       </c>
       <c r="AH8" t="n">
-        <v>101.7203285000287</v>
+        <v>88.79587699999684</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1802,31 +1802,31 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02293431534890115</v>
+        <v>0.02300442498685829</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03095238231160805</v>
+        <v>0.03104007649482944</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.519335532136671</v>
+        <v>1.526721829549781</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.5222799462085819</v>
+        <v>0.5267434459329313</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.986467558331141</v>
+        <v>1.215830683333479</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01529423054631075</v>
+        <v>0.01447457499954099</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.986467558331141</v>
+        <v>1.215830683333479</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01529423054631075</v>
+        <v>0.01447457499954099</v>
       </c>
       <c r="AH9" t="n">
-        <v>72.06342439958826</v>
+        <v>44.29098929998872</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1902,31 +1902,31 @@
         <v>20</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.04530625639889532</v>
+        <v>0.04553603915331625</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.05888166025740332</v>
+        <v>0.05926291108002088</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.918704761343044</v>
+        <v>2.95558735777936</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.5593043169575611</v>
+        <v>0.5623583090115495</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.8302703861134232</v>
+        <v>0.6232185499983542</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.007629058339969359</v>
+        <v>0.006903383333135732</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.8302703861134232</v>
+        <v>0.6232185499983542</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.007629058339969359</v>
+        <v>0.006903383333135732</v>
       </c>
       <c r="AH10" t="n">
-        <v>30.16438000032213</v>
+        <v>22.68438959993364</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2014,19 +2014,19 @@
         <v>0.4929430621681081</v>
       </c>
       <c r="AD11" t="n">
-        <v>6.950706977772319</v>
+        <v>6.381073338890322</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.07070434166234918</v>
+        <v>0.07396304999888847</v>
       </c>
       <c r="AF11" t="n">
-        <v>6.950706977772319</v>
+        <v>6.381073338890322</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.07070434166234918</v>
+        <v>0.07396304999888847</v>
       </c>
       <c r="AH11" t="n">
-        <v>252.7708074996481</v>
+        <v>232.3813100000116</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2102,31 +2102,31 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.02322126575123965</v>
+        <v>0.02306813769094355</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.03122548496312105</v>
+        <v>0.03114702623314099</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.540987453969507</v>
+        <v>1.533895710245983</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.5127746420440367</v>
+        <v>0.5156004622444423</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.084737086125338</v>
+        <v>3.087499386110317</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.03454104444244877</v>
+        <v>0.03834338333197391</v>
       </c>
       <c r="AF12" t="n">
-        <v>3.084737086125338</v>
+        <v>3.087499386110317</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.03454104444244877</v>
+        <v>0.03834338333197391</v>
       </c>
       <c r="AH12" t="n">
-        <v>112.2940127004404</v>
+        <v>112.5303396999225</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2202,31 +2202,31 @@
         <v>20</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.04525997207078123</v>
+        <v>0.04566622645336074</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.05873624250985902</v>
+        <v>0.05949218547445292</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.915566937179729</v>
+        <v>2.955404528488206</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.5603529446612857</v>
+        <v>0.5615718208870195</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.271665169427352</v>
+        <v>1.355275766665727</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.01837442500982434</v>
+        <v>0.02076342499842414</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.271665169427352</v>
+        <v>1.355275766665727</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01837442500982434</v>
+        <v>0.02076342499842414</v>
       </c>
       <c r="AH13" t="n">
-        <v>46.44142539973836</v>
+        <v>49.53741089990945</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2314,19 +2314,19 @@
         <v>0.4961933311016327</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.110392705566483</v>
+        <v>1.756426077777481</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.004584666655217814</v>
+        <v>0.006232058333908855</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.110392705566483</v>
+        <v>1.756426077777481</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.004584666655217814</v>
+        <v>0.006232058333908855</v>
       </c>
       <c r="AH14" t="n">
-        <v>40.13918539998122</v>
+        <v>63.45569290001004</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2402,31 +2402,31 @@
         <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.022865289224471</v>
+        <v>0.02285567401736972</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.03089766814762891</v>
+        <v>0.03088312624516037</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.513760049768619</v>
+        <v>1.514049298872743</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.5326981941869274</v>
+        <v>0.5282882472103155</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.5708775527891703</v>
+        <v>0.8835218222229742</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.002791094435249559</v>
+        <v>0.003506608335252774</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.5708775527891703</v>
+        <v>0.8835218222229742</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.002791094435249559</v>
+        <v>0.003506608335252774</v>
       </c>
       <c r="AH15" t="n">
-        <v>20.65207130007911</v>
+        <v>31.93302350009617</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2502,31 +2502,31 @@
         <v>20</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.04588278432810449</v>
+        <v>0.0458051624554171</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.05951194170106893</v>
+        <v>0.05950021666494285</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.993722260161309</v>
+        <v>3.017143828257542</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.5292457808209525</v>
+        <v>0.5197149572254463</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.3423084305541124</v>
+        <v>0.5335881444431532</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.001757016670631452</v>
+        <v>0.002185113888925925</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.3423084305541124</v>
+        <v>0.5335881444431532</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.001757016670631452</v>
+        <v>0.002185113888925925</v>
       </c>
       <c r="AH16" t="n">
-        <v>12.38635610009078</v>
+        <v>19.28783729995484</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2614,19 +2614,19 @@
         <v>0.4897181105943054</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.708315266671384</v>
+        <v>2.215259697221982</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.01020731112415281</v>
+        <v>0.01153624166585764</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.708315266671384</v>
+        <v>2.215259697221982</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.01020731112415281</v>
+        <v>0.01153624166585764</v>
       </c>
       <c r="AH17" t="n">
-        <v>61.86681280063931</v>
+        <v>80.16465379996225</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2702,31 +2702,31 @@
         <v>5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.02289654729308388</v>
+        <v>0.02288065790111407</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.03094810310529818</v>
+        <v>0.03093894597197183</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.517075100549925</v>
+        <v>1.518626246525013</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.5255601152165973</v>
+        <v>0.5293465844460337</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.8420179360934222</v>
+        <v>1.005588852778197</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.005936672241659834</v>
+        <v>0.005719572220388929</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.8420179360934222</v>
+        <v>1.005588852778197</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.005936672241659834</v>
+        <v>0.005719572220388929</v>
       </c>
       <c r="AH18" t="n">
-        <v>30.52636590006296</v>
+        <v>36.40710329994909</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2802,31 +2802,31 @@
         <v>20</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.04575383107311375</v>
+        <v>0.04561311526731179</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.05945268532618701</v>
+        <v>0.05926715315052091</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.966710061213149</v>
+        <v>2.996959643849763</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.5554480941937988</v>
+        <v>0.5258057484582801</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.4755706500145607</v>
+        <v>0.4741741749995627</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.003288602763657561</v>
+        <v>0.003796716667339853</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.4755706500145607</v>
+        <v>0.4741741749995627</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.003288602763657561</v>
+        <v>0.003796716667339853</v>
       </c>
       <c r="AH19" t="n">
-        <v>17.23893310001586</v>
+        <v>17.20695210000849</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2914,19 +2914,19 @@
         <v>0.4893574028376709</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.008591399990514</v>
+        <v>4.604528444444845</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.02564493612347481</v>
+        <v>0.02418226111209757</v>
       </c>
       <c r="AF20" t="n">
-        <v>4.008591399990514</v>
+        <v>4.604528444444845</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.02564493612347481</v>
+        <v>0.02418226111209757</v>
       </c>
       <c r="AH20" t="n">
-        <v>145.2325081001036</v>
+        <v>166.6335854000499</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3002,31 +3002,31 @@
         <v>5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.02289580552912028</v>
+        <v>0.02290336579125676</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.03091507504434747</v>
+        <v>0.03092590044867656</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.515163319661534</v>
+        <v>1.520340387575113</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.5257843675027275</v>
+        <v>0.5263105908806486</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.078765100000763</v>
+        <v>1.91642431666777</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.01363073889903414</v>
+        <v>0.01323710277857673</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.078765100000763</v>
+        <v>1.91642431666777</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.01363073889903414</v>
+        <v>0.01323710277857673</v>
       </c>
       <c r="AH21" t="n">
-        <v>75.32625020039268</v>
+        <v>69.4678111000685</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3102,31 +3102,31 @@
         <v>20</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.04573017921318567</v>
+        <v>0.0457846343589006</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.05932482507686635</v>
+        <v>0.05946647660395988</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.960853220476964</v>
+        <v>3.012211658395088</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.5391128401017127</v>
+        <v>0.528488959571554</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.059094722233971</v>
+        <v>0.9834281916656539</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.006658911110005445</v>
+        <v>0.006324774999989637</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.059094722233971</v>
+        <v>0.9834281916656539</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.006658911110005445</v>
+        <v>0.006324774999989637</v>
       </c>
       <c r="AH22" t="n">
-        <v>38.36713080038317</v>
+        <v>35.63110679996316</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3214,19 +3214,19 @@
         <v>0.4924998707550184</v>
       </c>
       <c r="AD23" t="n">
-        <v>7.955789294443094</v>
+        <v>7.029913069444672</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.06720180277867863</v>
+        <v>0.06498605277900221</v>
       </c>
       <c r="AF23" t="n">
-        <v>7.955789294443094</v>
+        <v>7.029913069444672</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.06720180277867863</v>
+        <v>0.06498605277900221</v>
       </c>
       <c r="AH23" t="n">
-        <v>288.8276794999838</v>
+        <v>255.4163684000523</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3302,31 +3302,31 @@
         <v>5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.02294599159304233</v>
+        <v>0.02303788334847278</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.03097855681183702</v>
+        <v>0.03107746339320202</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.520913310528536</v>
+        <v>1.529556644143107</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.5218455451234923</v>
+        <v>0.5161918521779466</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.07874023332584</v>
+        <v>3.217461150000114</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.04884970833599153</v>
+        <v>0.03399153333238145</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.07874023332584</v>
+        <v>3.217461150000114</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.04884970833599153</v>
+        <v>0.03399153333238145</v>
       </c>
       <c r="AH24" t="n">
-        <v>112.5932378998259</v>
+        <v>117.0522965999698</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3402,31 +3402,31 @@
         <v>20</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.04592037081572126</v>
+        <v>0.04633598861874327</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.05958116397227248</v>
+        <v>0.06011451111026168</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.968277160624526</v>
+        <v>3.023224779112003</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.5640173612115034</v>
+        <v>0.5360968146333068</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.355225174988542</v>
+        <v>1.379896699999032</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.01784451388650471</v>
+        <v>0.01607482222405249</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.355225174988542</v>
+        <v>1.379896699999032</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.01784451388650471</v>
+        <v>0.01607482222405249</v>
       </c>
       <c r="AH25" t="n">
-        <v>49.43050879950169</v>
+        <v>50.25497480003105</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
         <v>0.4961933311016327</v>
       </c>
       <c r="H2" t="n">
-        <v>1.110392705566483</v>
+        <v>1.756426077777481</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004584666655217814</v>
+        <v>0.006232058333908855</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3554,22 +3554,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.022865289224471</v>
+        <v>0.02285567401736972</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03089766814762891</v>
+        <v>0.03088312624516037</v>
       </c>
       <c r="F3" t="n">
-        <v>1.513760049768619</v>
+        <v>1.514049298872743</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5326981941869274</v>
+        <v>0.5282882472103155</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5708775527891703</v>
+        <v>0.8835218222229742</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002791094435249559</v>
+        <v>0.003506608335252774</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3588,26 +3588,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chaotic_lstm_g003</t>
+          <t>chaotic_lstm_g002</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04573017921318567</v>
+        <v>0.04561311526731179</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05932482507686635</v>
+        <v>0.05926715315052091</v>
       </c>
       <c r="F4" t="n">
-        <v>2.960853220476964</v>
+        <v>2.996959643849763</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5391128401017127</v>
+        <v>0.5258057484582801</v>
       </c>
       <c r="H4" t="n">
-        <v>1.059094722233971</v>
+        <v>0.4741741749995627</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006658911110005445</v>
+        <v>0.003796716667339853</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3642,10 +3642,10 @@
         <v>0.4955974999103683</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6562172305647336</v>
+        <v>0.6560983222225333</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005449558310728107</v>
+        <v>0.005193697222340335</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3668,22 +3668,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.0229090707835557</v>
+        <v>0.02288283647516584</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03095397412585692</v>
+        <v>0.03095820841866742</v>
       </c>
       <c r="F6" t="n">
-        <v>1.517823962689854</v>
+        <v>1.517340273475212</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5160058145289814</v>
+        <v>0.5273339110168891</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3593156472165395</v>
+        <v>0.3688642944438875</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003248872228949848</v>
+        <v>0.002982194444484776</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3702,26 +3702,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lstm_g004</t>
+          <t>lstm_g001</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04525997207078123</v>
+        <v>0.04551551390821578</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05873624250985902</v>
+        <v>0.05922351927863698</v>
       </c>
       <c r="F7" t="n">
-        <v>2.915566937179729</v>
+        <v>2.984057578068402</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5603529446612857</v>
+        <v>0.5436787536440352</v>
       </c>
       <c r="H7" t="n">
-        <v>1.271665169427352</v>
+        <v>0.2086646833332553</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01837442500982434</v>
+        <v>0.001698883332816574</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>0.6616667888754617</v>
+        <v>0.6612920194448736</v>
       </c>
       <c r="P2" t="n">
-        <v>1.114977372221701</v>
+        <v>1.76265813611139</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>0.453310583346239</v>
+        <v>1.101366116666516</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4085,14 +4085,14 @@
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>1.125568069436768</v>
+        <v>1.034581508332242</v>
       </c>
       <c r="P3" t="n">
-        <v>1.718522577795536</v>
+        <v>2.22679593888784</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0.5929545083587682</v>
+        <v>1.192214430555598</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
@@ -4142,7 +4142,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>2.825564680556353</v>
+        <v>2.466552138888801</v>
       </c>
       <c r="P4" t="n">
-        <v>4.034236336113988</v>
+        <v>4.628710705556943</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>1.208671655557635</v>
+        <v>2.162158566668142</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
@@ -4244,7 +4244,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4289,14 +4289,14 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>7.021411319434669</v>
+        <v>6.45503638888921</v>
       </c>
       <c r="P5" t="n">
-        <v>8.022991097221773</v>
+        <v>7.094899122223674</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>1.001579777787104</v>
+        <v>0.6398627333344633</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
@@ -4346,7 +4346,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4380,25 +4380,25 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.0229090707835557</v>
+        <v>0.02288283647516584</v>
       </c>
       <c r="K6" t="n">
-        <v>0.022865289224471</v>
+        <v>0.02285567401736972</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>-4.378155908469836e-05</v>
+        <v>-2.716245779612117e-05</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>0.3625645194454894</v>
+        <v>0.3718464888883723</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5736686472244199</v>
+        <v>0.8870284305582269</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>0.2111041277789305</v>
+        <v>0.5151819416698546</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
@@ -4448,7 +4448,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4482,25 +4482,25 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.02305557405202937</v>
+        <v>0.02304555264523576</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02289654729308388</v>
+        <v>0.02288065790111407</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>-0.0001590267589454894</v>
+        <v>-0.0001648947441216936</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>0.6122068750038225</v>
+        <v>0.5331695055570485</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8479546083350821</v>
+        <v>1.011308424998586</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>0.2357477333312595</v>
+        <v>0.4781389194415373</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
@@ -4550,7 +4550,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4584,25 +4584,25 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>0.02293431534890115</v>
+        <v>0.02300442498685829</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02289580552912028</v>
+        <v>0.02290336579125676</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>-3.85098197808742e-05</v>
+        <v>-0.0001010591956015217</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>2.001761788877451</v>
+        <v>1.23030525833302</v>
       </c>
       <c r="P8" t="n">
-        <v>2.092395838899797</v>
+        <v>1.929661419446347</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>0.09063405002234504</v>
+        <v>0.6993561611133272</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4686,25 +4686,25 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>0.02322126575123965</v>
+        <v>0.02306813769094355</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02294599159304233</v>
+        <v>0.02303788334847278</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>-0.0002752741581973223</v>
+        <v>-3.025434247076741e-05</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>3.119278130567787</v>
+        <v>3.125842769442291</v>
       </c>
       <c r="P9" t="n">
-        <v>3.127589941661831</v>
+        <v>3.251452683332495</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>0.008311811094043886</v>
+        <v>0.1256099138902047</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
@@ -4754,7 +4754,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4788,25 +4788,25 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>0.04526260267618217</v>
+        <v>0.04551551390821578</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04588278432810449</v>
+        <v>0.0458051624554171</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0.0006201816519223191</v>
+        <v>0.0002896485472013224</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>0.2389726944481178</v>
+        <v>0.2103635666660718</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3440654472247439</v>
+        <v>0.5357732583320791</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>0.1050927527766261</v>
+        <v>0.3254096916660073</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
@@ -4856,7 +4856,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4890,25 +4890,25 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>0.04574416318638141</v>
+        <v>0.04555148313884066</v>
       </c>
       <c r="K11" t="n">
-        <v>0.04575383107311375</v>
+        <v>0.04561311526731179</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>9.667886732345199e-06</v>
+        <v>6.163212847113547e-05</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>0.4169987250093578</v>
+        <v>0.2696341722197152</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4788592527782182</v>
+        <v>0.4779708916669025</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>0.06186052776886042</v>
+        <v>0.2083367194471873</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
@@ -4958,7 +4958,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -4992,25 +4992,25 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>0.04530625639889532</v>
+        <v>0.04553603915331625</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04573017921318567</v>
+        <v>0.0457846343589006</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>0.0004239228142903506</v>
+        <v>0.0002485952055843524</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>0.8378994444533926</v>
+        <v>0.63012193333149</v>
       </c>
       <c r="P12" t="n">
-        <v>1.065753633343977</v>
+        <v>0.9897529666656435</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>0.2278541888905842</v>
+        <v>0.3596310333341535</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
@@ -5060,7 +5060,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5094,25 +5094,25 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0.04525997207078123</v>
+        <v>0.04566622645336074</v>
       </c>
       <c r="K13" t="n">
-        <v>0.04592037081572126</v>
+        <v>0.04633598861874327</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>0.0006603987449400328</v>
+        <v>0.0006697621653825314</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>1.290039594437177</v>
+        <v>1.376039191664151</v>
       </c>
       <c r="P13" t="n">
-        <v>1.373069688875047</v>
+        <v>1.395971522223085</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>0.08303009443787035</v>
+        <v>0.01993233055893362</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
@@ -5238,7 +5238,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5248,33 +5248,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>chaotic_lstm_g003</t>
+          <t>chaotic_lstm_g002</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.02631610738831531</v>
+        <v>0.02626834077593868</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03483539149928175</v>
+        <v>0.03482177650678748</v>
       </c>
       <c r="F2" t="n">
-        <v>1.71772321853742</v>
+        <v>1.730576619310517</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5180848701473703</v>
+        <v>0.5149568144995397</v>
       </c>
       <c r="H2" t="n">
-        <v>2.382150407408416</v>
+        <v>1.231674241666581</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01531152871083813</v>
+        <v>0.007017510184528807</v>
       </c>
       <c r="J2" t="n">
-        <v>86.30862970029314</v>
+        <v>44.59290306663994</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>lstm_grp_003</t>
+          <t>lstm_grp_002</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -5286,7 +5286,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5300,25 +5300,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.02616428792103205</v>
+        <v>0.02623984689557997</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03468600839465527</v>
+        <v>0.03481656310059256</v>
       </c>
       <c r="F3" t="n">
-        <v>1.708343244637535</v>
+        <v>1.725998206960399</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5257469268673777</v>
+        <v>0.5222033881904308</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4175126138940902</v>
+        <v>0.411209099999892</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003555387028932779</v>
+        <v>0.003291591666547228</v>
       </c>
       <c r="J3" t="n">
-        <v>15.15844803322883</v>
+        <v>14.92202489999181</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>architecture_tuning_lstm_v1_20260329T170046Z</t>
+          <t>architecture_tuning_lstm_v1_20260819T072001Z</t>
         </is>
       </c>
     </row>
